--- a/Avaliações dos Itens/Avaliações (2008-2024)/2009.xlsx
+++ b/Avaliações dos Itens/Avaliações (2008-2024)/2009.xlsx
@@ -2,13 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1a040bb1f01841a5/Desktop/Educomp 2026/Análises/Avaliação 1/criterios por questoes e provas/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{B3A39223-99B3-4034-A9D0-78F4900501ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7E0AC9FA-9E51-413C-9757-CD289D3703B9}"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{B3A39223-99B3-4034-A9D0-78F4900501ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53D81845-02BB-491A-A1E1-95B0327390DF}"/>
   <bookViews>
     <workbookView xWindow="29388" yWindow="-81" windowWidth="29698" windowHeight="16094" xr2:uid="{8FF54422-96D6-49D5-8E2B-0CBEDE1A85D3}"/>
   </bookViews>
@@ -132,16 +127,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -160,10 +153,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -491,13 +480,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -505,7 +494,7 @@
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -516,7 +505,7 @@
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -527,7 +516,7 @@
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -538,7 +527,7 @@
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -549,7 +538,7 @@
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -560,7 +549,7 @@
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -571,7 +560,7 @@
       <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -582,7 +571,7 @@
       <c r="A9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -593,7 +582,7 @@
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -604,7 +593,7 @@
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -615,7 +604,7 @@
       <c r="A12" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -626,7 +615,7 @@
       <c r="A13" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -637,7 +626,7 @@
       <c r="A14" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -648,7 +637,7 @@
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -659,7 +648,7 @@
       <c r="A16" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -670,7 +659,7 @@
       <c r="A17" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -681,7 +670,7 @@
       <c r="A18" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -692,7 +681,7 @@
       <c r="A19" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -703,7 +692,7 @@
       <c r="A20" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -714,274 +703,67 @@
       <c r="A21" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="2"/>
-    </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="2"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="2"/>
-    </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="2"/>
-    </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="2"/>
-    </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="2"/>
-    </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="2"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="2"/>
-    </row>
-    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="2"/>
-    </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="2"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="2"/>
-    </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="2"/>
-    </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="2"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="2"/>
-    </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="2"/>
-    </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="2"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="2"/>
-    </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="2"/>
-    </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="2"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="2"/>
-    </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="2"/>
-    </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="2"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="2"/>
-    </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="2"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="2"/>
-    </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="2"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="2"/>
-    </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="2"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="2"/>
-    </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="2"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="2"/>
-    </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="2"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="2"/>
-    </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="2"/>
-    </row>
-    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="2"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="2"/>
-    </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="2"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="2"/>
-    </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="2"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="2"/>
-    </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="2"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="2"/>
-    </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="2"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="2"/>
-    </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="2"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="2"/>
-    </row>
-    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="2"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="2"/>
-    </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="2"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="2"/>
-    </row>
-    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="2"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="2"/>
-    </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="2"/>
-      <c r="B61" s="4"/>
-      <c r="C61" s="2"/>
-    </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="1"/>
-      <c r="B62" s="4"/>
-      <c r="C62" s="2"/>
-    </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="1"/>
-      <c r="B63" s="4"/>
-      <c r="C63" s="2"/>
-    </row>
-    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="1"/>
-      <c r="B64" s="4"/>
-      <c r="C64" s="2"/>
-    </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="1"/>
-      <c r="B65" s="4"/>
-      <c r="C65" s="2"/>
-    </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="1"/>
-      <c r="B66" s="4"/>
-      <c r="C66" s="2"/>
-    </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="1"/>
-      <c r="B67" s="4"/>
-      <c r="C67" s="2"/>
-    </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="1"/>
-      <c r="B68" s="4"/>
-      <c r="C68" s="2"/>
-    </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="1"/>
-      <c r="B69" s="4"/>
-      <c r="C69" s="2"/>
-    </row>
-    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="1"/>
-      <c r="B70" s="4"/>
-      <c r="C70" s="2"/>
-    </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="2"/>
-      <c r="B71" s="4"/>
-      <c r="C71" s="2"/>
-    </row>
-    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="2"/>
-      <c r="B72" s="4"/>
-      <c r="C72" s="2"/>
-    </row>
-    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="2"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="2"/>
-    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3"/>
+    <row r="33" x14ac:dyDescent="0.3"/>
+    <row r="34" x14ac:dyDescent="0.3"/>
+    <row r="35" x14ac:dyDescent="0.3"/>
+    <row r="36" x14ac:dyDescent="0.3"/>
+    <row r="37" x14ac:dyDescent="0.3"/>
+    <row r="38" x14ac:dyDescent="0.3"/>
+    <row r="39" x14ac:dyDescent="0.3"/>
+    <row r="40" x14ac:dyDescent="0.3"/>
+    <row r="41" x14ac:dyDescent="0.3"/>
+    <row r="42" x14ac:dyDescent="0.3"/>
+    <row r="43" x14ac:dyDescent="0.3"/>
+    <row r="44" x14ac:dyDescent="0.3"/>
+    <row r="45" x14ac:dyDescent="0.3"/>
+    <row r="46" x14ac:dyDescent="0.3"/>
+    <row r="47" x14ac:dyDescent="0.3"/>
+    <row r="48" x14ac:dyDescent="0.3"/>
+    <row r="49" x14ac:dyDescent="0.3"/>
+    <row r="50" x14ac:dyDescent="0.3"/>
+    <row r="51" x14ac:dyDescent="0.3"/>
+    <row r="52" x14ac:dyDescent="0.3"/>
+    <row r="53" x14ac:dyDescent="0.3"/>
+    <row r="54" x14ac:dyDescent="0.3"/>
+    <row r="55" x14ac:dyDescent="0.3"/>
+    <row r="56" x14ac:dyDescent="0.3"/>
+    <row r="57" x14ac:dyDescent="0.3"/>
+    <row r="58" x14ac:dyDescent="0.3"/>
+    <row r="59" x14ac:dyDescent="0.3"/>
+    <row r="60" x14ac:dyDescent="0.3"/>
+    <row r="61" x14ac:dyDescent="0.3"/>
+    <row r="62" x14ac:dyDescent="0.3"/>
+    <row r="63" x14ac:dyDescent="0.3"/>
+    <row r="64" x14ac:dyDescent="0.3"/>
+    <row r="65" x14ac:dyDescent="0.3"/>
+    <row r="66" x14ac:dyDescent="0.3"/>
+    <row r="67" x14ac:dyDescent="0.3"/>
+    <row r="68" x14ac:dyDescent="0.3"/>
+    <row r="69" x14ac:dyDescent="0.3"/>
+    <row r="70" x14ac:dyDescent="0.3"/>
+    <row r="71" x14ac:dyDescent="0.3"/>
+    <row r="72" x14ac:dyDescent="0.3"/>
+    <row r="73" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>